--- a/output/yearly_total_coral_cover_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_16_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255259114931053</v>
+        <v>1.286940113347098</v>
       </c>
       <c r="C3" t="n">
-        <v>4.645951059055357</v>
+        <v>4.639540246546625</v>
       </c>
       <c r="D3" t="n">
-        <v>6.100280895074524</v>
+        <v>6.186841590157966</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00149106906093</v>
+        <v>12.11332195005169</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378302477826739</v>
+        <v>1.461339199327805</v>
       </c>
       <c r="C4" t="n">
-        <v>5.158904376965492</v>
+        <v>5.143047152738148</v>
       </c>
       <c r="D4" t="n">
-        <v>6.361317683842396</v>
+        <v>6.593596939575636</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89852453863463</v>
+        <v>13.19798329164159</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.54957053739352</v>
+        <v>1.696184780717269</v>
       </c>
       <c r="C5" t="n">
-        <v>5.859589404553725</v>
+        <v>5.784332472205191</v>
       </c>
       <c r="D5" t="n">
-        <v>6.639618026913998</v>
+        <v>7.113844546896976</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04877796886124</v>
+        <v>14.59436179981944</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.745108600785043</v>
+        <v>1.9515953825965</v>
       </c>
       <c r="C6" t="n">
-        <v>6.710482599781857</v>
+        <v>6.547426958234088</v>
       </c>
       <c r="D6" t="n">
-        <v>6.978566932557278</v>
+        <v>7.649169116984101</v>
       </c>
       <c r="E6" t="n">
-        <v>15.43415813312418</v>
+        <v>16.14819145781469</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.977751528494822</v>
+        <v>2.243036287021197</v>
       </c>
       <c r="C7" t="n">
-        <v>7.751351110390001</v>
+        <v>7.475573437492782</v>
       </c>
       <c r="D7" t="n">
-        <v>7.312392066003896</v>
+        <v>8.23294213853856</v>
       </c>
       <c r="E7" t="n">
-        <v>17.04149470488872</v>
+        <v>17.95155186305254</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.232911749076773</v>
+        <v>1.422491828125447</v>
       </c>
       <c r="C8" t="n">
-        <v>5.440277546959172</v>
+        <v>5.132907215750013</v>
       </c>
       <c r="D8" t="n">
-        <v>5.626236751906646</v>
+        <v>6.525329867521598</v>
       </c>
       <c r="E8" t="n">
-        <v>12.29942604794259</v>
+        <v>13.08072891139706</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.565523396021127</v>
+        <v>1.786268833259122</v>
       </c>
       <c r="C9" t="n">
-        <v>6.724792611991292</v>
+        <v>6.297780815875442</v>
       </c>
       <c r="D9" t="n">
-        <v>6.240152023531469</v>
+        <v>7.251830478565323</v>
       </c>
       <c r="E9" t="n">
-        <v>14.53046803154389</v>
+        <v>15.33588012769989</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.91662112892737</v>
+        <v>2.154474364721486</v>
       </c>
       <c r="C10" t="n">
-        <v>8.146928102552762</v>
+        <v>7.593389108825242</v>
       </c>
       <c r="D10" t="n">
-        <v>6.764422570158822</v>
+        <v>7.950537376277429</v>
       </c>
       <c r="E10" t="n">
-        <v>16.82797180163895</v>
+        <v>17.69840084982416</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.272152675034286</v>
+        <v>2.510539562420874</v>
       </c>
       <c r="C11" t="n">
-        <v>9.651397712910702</v>
+        <v>9.018643853340956</v>
       </c>
       <c r="D11" t="n">
-        <v>7.284921565289533</v>
+        <v>8.640474052967532</v>
       </c>
       <c r="E11" t="n">
-        <v>19.20847195323452</v>
+        <v>20.16965746872936</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.637483543090469</v>
+        <v>2.864825379863757</v>
       </c>
       <c r="C12" t="n">
-        <v>11.17958984749983</v>
+        <v>10.49071928442386</v>
       </c>
       <c r="D12" t="n">
-        <v>7.837489102759057</v>
+        <v>9.242849622340117</v>
       </c>
       <c r="E12" t="n">
-        <v>21.65456249334935</v>
+        <v>22.59839428662773</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.986722091927359</v>
+        <v>3.203690673224891</v>
       </c>
       <c r="C13" t="n">
-        <v>12.75383721069885</v>
+        <v>11.97199601097292</v>
       </c>
       <c r="D13" t="n">
-        <v>8.356658738560633</v>
+        <v>9.968175957377587</v>
       </c>
       <c r="E13" t="n">
-        <v>24.09721804118684</v>
+        <v>25.1438626415754</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.706797836264208</v>
+        <v>1.841464168855742</v>
       </c>
       <c r="C14" t="n">
-        <v>8.908172501317665</v>
+        <v>8.363911209037319</v>
       </c>
       <c r="D14" t="n">
-        <v>6.373476643539165</v>
+        <v>7.488535868545651</v>
       </c>
       <c r="E14" t="n">
-        <v>16.98844698112104</v>
+        <v>17.69391124643871</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.766164119940012</v>
+        <v>1.885976609766293</v>
       </c>
       <c r="C15" t="n">
-        <v>9.550019515400145</v>
+        <v>8.998532560016542</v>
       </c>
       <c r="D15" t="n">
-        <v>6.419412618620875</v>
+        <v>7.625312958701318</v>
       </c>
       <c r="E15" t="n">
-        <v>17.73559625396103</v>
+        <v>18.50982212848415</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.06759011757491</v>
+        <v>2.197328076691126</v>
       </c>
       <c r="C16" t="n">
-        <v>11.19603735129443</v>
+        <v>10.57383510877393</v>
       </c>
       <c r="D16" t="n">
-        <v>6.882522645668179</v>
+        <v>8.272647942450535</v>
       </c>
       <c r="E16" t="n">
-        <v>20.14615011453752</v>
+        <v>21.04381112791559</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.675342639820139</v>
+        <v>1.771573549790412</v>
       </c>
       <c r="C17" t="n">
-        <v>10.22724871674368</v>
+        <v>9.704144087489853</v>
       </c>
       <c r="D17" t="n">
-        <v>6.401564445357667</v>
+        <v>7.796323591304068</v>
       </c>
       <c r="E17" t="n">
-        <v>18.30415580192149</v>
+        <v>19.27204122858433</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.922713608859209</v>
+        <v>2.017334452594516</v>
       </c>
       <c r="C18" t="n">
-        <v>11.88219063926957</v>
+        <v>11.24697042219076</v>
       </c>
       <c r="D18" t="n">
-        <v>6.854110867107277</v>
+        <v>8.397732417448621</v>
       </c>
       <c r="E18" t="n">
-        <v>20.65901511523606</v>
+        <v>21.66203729223389</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.943320493171349</v>
+        <v>2.016784673880138</v>
       </c>
       <c r="C19" t="n">
-        <v>12.65515987673125</v>
+        <v>11.98464582968477</v>
       </c>
       <c r="D19" t="n">
-        <v>6.950940643177141</v>
+        <v>8.583783424880433</v>
       </c>
       <c r="E19" t="n">
-        <v>21.54942101307974</v>
+        <v>22.58521392844534</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.181266684249648</v>
+        <v>2.237422652932566</v>
       </c>
       <c r="C20" t="n">
-        <v>14.48910385817247</v>
+        <v>13.73660406034433</v>
       </c>
       <c r="D20" t="n">
-        <v>7.366848240604259</v>
+        <v>9.167471704963335</v>
       </c>
       <c r="E20" t="n">
-        <v>24.03721878302638</v>
+        <v>25.14149841824023</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.300786255695896</v>
+        <v>1.327342531095772</v>
       </c>
       <c r="C21" t="n">
-        <v>10.62186220646569</v>
+        <v>10.08743802618189</v>
       </c>
       <c r="D21" t="n">
-        <v>6.154900334665656</v>
+        <v>7.711795113968418</v>
       </c>
       <c r="E21" t="n">
-        <v>18.07754879682724</v>
+        <v>19.12657567124608</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_16_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.286940113347098</v>
+        <v>1.247218601233272</v>
       </c>
       <c r="C3" t="n">
-        <v>4.639540246546625</v>
+        <v>4.604707837999949</v>
       </c>
       <c r="D3" t="n">
-        <v>6.186841590157966</v>
+        <v>6.07930094663477</v>
       </c>
       <c r="E3" t="n">
-        <v>12.11332195005169</v>
+        <v>11.93122738586799</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.461339199327805</v>
+        <v>1.35641175557694</v>
       </c>
       <c r="C4" t="n">
-        <v>5.143047152738148</v>
+        <v>5.07279956589571</v>
       </c>
       <c r="D4" t="n">
-        <v>6.593596939575636</v>
+        <v>6.403082651067166</v>
       </c>
       <c r="E4" t="n">
-        <v>13.19798329164159</v>
+        <v>12.83229397253982</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.696184780717269</v>
+        <v>1.507048027708655</v>
       </c>
       <c r="C5" t="n">
-        <v>5.784332472205191</v>
+        <v>5.646687819287876</v>
       </c>
       <c r="D5" t="n">
-        <v>7.113844546896976</v>
+        <v>6.724112799776676</v>
       </c>
       <c r="E5" t="n">
-        <v>14.59436179981944</v>
+        <v>13.87784864677321</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.9515953825965</v>
+        <v>1.67471076679483</v>
       </c>
       <c r="C6" t="n">
-        <v>6.547426958234088</v>
+        <v>6.40139550078502</v>
       </c>
       <c r="D6" t="n">
-        <v>7.649169116984101</v>
+        <v>7.080275019386238</v>
       </c>
       <c r="E6" t="n">
-        <v>16.14819145781469</v>
+        <v>15.15638128696609</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.243036287021197</v>
+        <v>1.866554148553143</v>
       </c>
       <c r="C7" t="n">
-        <v>7.475573437492782</v>
+        <v>7.320233585871985</v>
       </c>
       <c r="D7" t="n">
-        <v>8.23294213853856</v>
+        <v>7.414599586295578</v>
       </c>
       <c r="E7" t="n">
-        <v>17.95155186305254</v>
+        <v>16.6013873207207</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.422491828125447</v>
+        <v>1.113612092326453</v>
       </c>
       <c r="C8" t="n">
-        <v>5.132907215750013</v>
+        <v>5.098867120405145</v>
       </c>
       <c r="D8" t="n">
-        <v>6.525329867521598</v>
+        <v>5.66279877961511</v>
       </c>
       <c r="E8" t="n">
-        <v>13.08072891139706</v>
+        <v>11.87527799234671</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.786268833259122</v>
+        <v>1.396705614520978</v>
       </c>
       <c r="C9" t="n">
-        <v>6.297780815875442</v>
+        <v>6.357935638565816</v>
       </c>
       <c r="D9" t="n">
-        <v>7.251830478565323</v>
+        <v>6.234063388533484</v>
       </c>
       <c r="E9" t="n">
-        <v>15.33588012769989</v>
+        <v>13.98870464162028</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.154474364721486</v>
+        <v>1.682713328318078</v>
       </c>
       <c r="C10" t="n">
-        <v>7.593389108825242</v>
+        <v>7.796911740463358</v>
       </c>
       <c r="D10" t="n">
-        <v>7.950537376277429</v>
+        <v>6.695595646018631</v>
       </c>
       <c r="E10" t="n">
-        <v>17.69840084982416</v>
+        <v>16.17522071480007</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.510539562420874</v>
+        <v>1.960841129395282</v>
       </c>
       <c r="C11" t="n">
-        <v>9.018643853340956</v>
+        <v>9.374574402553467</v>
       </c>
       <c r="D11" t="n">
-        <v>8.640474052967532</v>
+        <v>7.258669137293213</v>
       </c>
       <c r="E11" t="n">
-        <v>20.16965746872936</v>
+        <v>18.59408466924196</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.864825379863757</v>
+        <v>2.234714347398684</v>
       </c>
       <c r="C12" t="n">
-        <v>10.49071928442386</v>
+        <v>11.02721351680599</v>
       </c>
       <c r="D12" t="n">
-        <v>9.242849622340117</v>
+        <v>7.816011734805777</v>
       </c>
       <c r="E12" t="n">
-        <v>22.59839428662773</v>
+        <v>21.07793959901045</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.203690673224891</v>
+        <v>2.498135567751889</v>
       </c>
       <c r="C13" t="n">
-        <v>11.97199601097292</v>
+        <v>12.73795303909333</v>
       </c>
       <c r="D13" t="n">
-        <v>9.968175957377587</v>
+        <v>8.307545384191986</v>
       </c>
       <c r="E13" t="n">
-        <v>25.1438626415754</v>
+        <v>23.5436339910372</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.841464168855742</v>
+        <v>1.440056985020349</v>
       </c>
       <c r="C14" t="n">
-        <v>8.363911209037319</v>
+        <v>8.869658538880064</v>
       </c>
       <c r="D14" t="n">
-        <v>7.488535868545651</v>
+        <v>6.308396588224645</v>
       </c>
       <c r="E14" t="n">
-        <v>17.69391124643871</v>
+        <v>16.61811211212506</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.885976609766293</v>
+        <v>1.451337266142145</v>
       </c>
       <c r="C15" t="n">
-        <v>8.998532560016542</v>
+        <v>9.677656534429275</v>
       </c>
       <c r="D15" t="n">
-        <v>7.625312958701318</v>
+        <v>6.348805323731443</v>
       </c>
       <c r="E15" t="n">
-        <v>18.50982212848415</v>
+        <v>17.47779912430286</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.197328076691126</v>
+        <v>1.658112967610608</v>
       </c>
       <c r="C16" t="n">
-        <v>10.57383510877393</v>
+        <v>11.48820546807828</v>
       </c>
       <c r="D16" t="n">
-        <v>8.272647942450535</v>
+        <v>6.884211251719484</v>
       </c>
       <c r="E16" t="n">
-        <v>21.04381112791559</v>
+        <v>20.03052968740838</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.771573549790412</v>
+        <v>1.313293721448001</v>
       </c>
       <c r="C17" t="n">
-        <v>9.704144087489853</v>
+        <v>10.63740327262391</v>
       </c>
       <c r="D17" t="n">
-        <v>7.796323591304068</v>
+        <v>6.415721247252907</v>
       </c>
       <c r="E17" t="n">
-        <v>19.27204122858433</v>
+        <v>18.36641824132482</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.017334452594516</v>
+        <v>1.478001533789488</v>
       </c>
       <c r="C18" t="n">
-        <v>11.24697042219076</v>
+        <v>12.45937974955036</v>
       </c>
       <c r="D18" t="n">
-        <v>8.397732417448621</v>
+        <v>6.867570628132501</v>
       </c>
       <c r="E18" t="n">
-        <v>21.66203729223389</v>
+        <v>20.80495191147235</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.016784673880138</v>
+        <v>1.465346805881747</v>
       </c>
       <c r="C19" t="n">
-        <v>11.98464582968477</v>
+        <v>13.36865483826966</v>
       </c>
       <c r="D19" t="n">
-        <v>8.583783424880433</v>
+        <v>6.986656624657638</v>
       </c>
       <c r="E19" t="n">
-        <v>22.58521392844534</v>
+        <v>21.82065826880905</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.237422652932566</v>
+        <v>1.611116705008313</v>
       </c>
       <c r="C20" t="n">
-        <v>13.73660406034433</v>
+        <v>15.36085654963547</v>
       </c>
       <c r="D20" t="n">
-        <v>9.167471704963335</v>
+        <v>7.44458302382652</v>
       </c>
       <c r="E20" t="n">
-        <v>25.14149841824023</v>
+        <v>24.4165562784703</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.327342531095772</v>
+        <v>0.948918061016797</v>
       </c>
       <c r="C21" t="n">
-        <v>10.08743802618189</v>
+        <v>11.25935026074131</v>
       </c>
       <c r="D21" t="n">
-        <v>7.711795113968418</v>
+        <v>6.228492142575996</v>
       </c>
       <c r="E21" t="n">
-        <v>19.12657567124608</v>
+        <v>18.4367604643341</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_16_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.247218601233272</v>
+        <v>2.632251649033035</v>
       </c>
       <c r="C3" t="n">
-        <v>4.604707837999949</v>
+        <v>7.721315236056117</v>
       </c>
       <c r="D3" t="n">
-        <v>6.07930094663477</v>
+        <v>8.207595144624563</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93122738586799</v>
+        <v>18.56116202971371</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.35641175557694</v>
+        <v>1.152545406924338</v>
       </c>
       <c r="C4" t="n">
-        <v>5.07279956589571</v>
+        <v>4.539252508914252</v>
       </c>
       <c r="D4" t="n">
-        <v>6.403082651067166</v>
+        <v>5.829352345076925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83229397253982</v>
+        <v>11.52115026091552</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.507048027708655</v>
+        <v>1.305162587384856</v>
       </c>
       <c r="C5" t="n">
-        <v>5.646687819287876</v>
+        <v>5.227449511207406</v>
       </c>
       <c r="D5" t="n">
-        <v>6.724112799776676</v>
+        <v>6.180021259677621</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87784864677321</v>
+        <v>12.71263335826988</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.67471076679483</v>
+        <v>1.468837292768249</v>
       </c>
       <c r="C6" t="n">
-        <v>6.40139550078502</v>
+        <v>6.082336654360583</v>
       </c>
       <c r="D6" t="n">
-        <v>7.080275019386238</v>
+        <v>6.578119560419803</v>
       </c>
       <c r="E6" t="n">
-        <v>15.15638128696609</v>
+        <v>14.12929350754863</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.866554148553143</v>
+        <v>1.63857909355085</v>
       </c>
       <c r="C7" t="n">
-        <v>7.320233585871985</v>
+        <v>7.061516548477528</v>
       </c>
       <c r="D7" t="n">
-        <v>7.414599586295578</v>
+        <v>7.066503293785929</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6013873207207</v>
+        <v>15.76659893581431</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.113612092326453</v>
+        <v>1.808155462836782</v>
       </c>
       <c r="C8" t="n">
-        <v>5.098867120405145</v>
+        <v>8.164776844899334</v>
       </c>
       <c r="D8" t="n">
-        <v>5.66279877961511</v>
+        <v>7.63136347732527</v>
       </c>
       <c r="E8" t="n">
-        <v>11.87527799234671</v>
+        <v>17.60429578506139</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.396705614520978</v>
+        <v>1.959727881654982</v>
       </c>
       <c r="C9" t="n">
-        <v>6.357935638565816</v>
+        <v>9.388431073875608</v>
       </c>
       <c r="D9" t="n">
-        <v>6.234063388533484</v>
+        <v>8.092291787007055</v>
       </c>
       <c r="E9" t="n">
-        <v>13.98870464162028</v>
+        <v>19.44045074253765</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.682713328318078</v>
+        <v>1.193834660795249</v>
       </c>
       <c r="C10" t="n">
-        <v>7.796911740463358</v>
+        <v>6.904189817500906</v>
       </c>
       <c r="D10" t="n">
-        <v>6.695595646018631</v>
+        <v>6.401211016184138</v>
       </c>
       <c r="E10" t="n">
-        <v>16.17522071480007</v>
+        <v>14.49923549448029</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.960841129395282</v>
+        <v>1.129834527955399</v>
       </c>
       <c r="C11" t="n">
-        <v>9.374574402553467</v>
+        <v>7.323602254232187</v>
       </c>
       <c r="D11" t="n">
-        <v>7.258669137293213</v>
+        <v>6.333411519728854</v>
       </c>
       <c r="E11" t="n">
-        <v>18.59408466924196</v>
+        <v>14.78684830191644</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.234714347398684</v>
+        <v>1.230198595760551</v>
       </c>
       <c r="C12" t="n">
-        <v>11.02721351680599</v>
+        <v>8.615876757332263</v>
       </c>
       <c r="D12" t="n">
-        <v>7.816011734805777</v>
+        <v>6.82361778341337</v>
       </c>
       <c r="E12" t="n">
-        <v>21.07793959901045</v>
+        <v>16.66969313650618</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.498135567751889</v>
+        <v>0.9696133026223198</v>
       </c>
       <c r="C13" t="n">
-        <v>12.73795303909333</v>
+        <v>8.15595741032376</v>
       </c>
       <c r="D13" t="n">
-        <v>8.307545384191986</v>
+        <v>6.300954940626454</v>
       </c>
       <c r="E13" t="n">
-        <v>23.5436339910372</v>
+        <v>15.42652565357253</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.440056985020349</v>
+        <v>1.054956630552495</v>
       </c>
       <c r="C14" t="n">
-        <v>8.869658538880064</v>
+        <v>9.507686554393022</v>
       </c>
       <c r="D14" t="n">
-        <v>6.308396588224645</v>
+        <v>6.780234352362704</v>
       </c>
       <c r="E14" t="n">
-        <v>16.61811211212506</v>
+        <v>17.34287753730822</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.451337266142145</v>
+        <v>1.026898281165121</v>
       </c>
       <c r="C15" t="n">
-        <v>9.677656534429275</v>
+        <v>10.22034703038283</v>
       </c>
       <c r="D15" t="n">
-        <v>6.348805323731443</v>
+        <v>6.897484480680901</v>
       </c>
       <c r="E15" t="n">
-        <v>17.47779912430286</v>
+        <v>18.14472979222885</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.658112967610608</v>
+        <v>1.125868267230242</v>
       </c>
       <c r="C16" t="n">
-        <v>11.48820546807828</v>
+        <v>11.84803563663882</v>
       </c>
       <c r="D16" t="n">
-        <v>6.884211251719484</v>
+        <v>7.415002965497565</v>
       </c>
       <c r="E16" t="n">
-        <v>20.03052968740838</v>
+        <v>20.38890686936663</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.313293721448001</v>
+        <v>0.67406797373586</v>
       </c>
       <c r="C17" t="n">
-        <v>10.63740327262391</v>
+        <v>8.836563823769904</v>
       </c>
       <c r="D17" t="n">
-        <v>6.415721247252907</v>
+        <v>6.226440289874121</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36641824132482</v>
+        <v>15.73707208737989</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.478001533789488</v>
+        <v>0.5361127863350982</v>
       </c>
       <c r="C18" t="n">
-        <v>12.45937974955036</v>
+        <v>7.752999065115657</v>
       </c>
       <c r="D18" t="n">
-        <v>6.867570628132501</v>
+        <v>5.773834963262257</v>
       </c>
       <c r="E18" t="n">
-        <v>20.80495191147235</v>
+        <v>14.06294681471301</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.465346805881747</v>
+        <v>0.6333254440096174</v>
       </c>
       <c r="C19" t="n">
-        <v>13.36865483826966</v>
+        <v>9.508776294344736</v>
       </c>
       <c r="D19" t="n">
-        <v>6.986656624657638</v>
+        <v>6.397146580688556</v>
       </c>
       <c r="E19" t="n">
-        <v>21.82065826880905</v>
+        <v>16.53924831904291</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.611116705008313</v>
+        <v>0.7282015421480292</v>
       </c>
       <c r="C20" t="n">
-        <v>15.36085654963547</v>
+        <v>11.37828899511081</v>
       </c>
       <c r="D20" t="n">
-        <v>7.44458302382652</v>
+        <v>7.082514470500297</v>
       </c>
       <c r="E20" t="n">
-        <v>24.4165562784703</v>
+        <v>19.18900500775914</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.948918061016797</v>
+        <v>0.8125533048969151</v>
       </c>
       <c r="C21" t="n">
-        <v>11.25935026074131</v>
+        <v>13.26859511225283</v>
       </c>
       <c r="D21" t="n">
-        <v>6.228492142575996</v>
+        <v>7.629711188416342</v>
       </c>
       <c r="E21" t="n">
-        <v>18.4367604643341</v>
+        <v>21.71085960556609</v>
       </c>
     </row>
   </sheetData>
